--- a/Supplementary Table S5.xlsx
+++ b/Supplementary Table S5.xlsx
@@ -5,20 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\profe\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\profe\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75DC658B-9D6C-4118-9482-5A329635418F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10246A4-967D-42D6-AC61-65F1F291F478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{EEC30A6C-0D93-4BED-94E8-BBA95C64BC6D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EEC30A6C-0D93-4BED-94E8-BBA95C64BC6D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Supplementary Table S5" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$C$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja2!$A$1:$D$359</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Supplementary Table S5'!$A$1:$D$359</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,21 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="98">
-  <si>
-    <t>Cepa</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="56">
   <si>
     <t>ST</t>
   </si>
   <si>
-    <t>saureus</t>
-  </si>
-  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>Isolation date</t>
   </si>
   <si>
     <t>2424_final</t>
@@ -92,15 +81,6 @@
   </si>
   <si>
     <t>CEU1</t>
-  </si>
-  <si>
-    <t>CEU19</t>
-  </si>
-  <si>
-    <t>CEU390</t>
-  </si>
-  <si>
-    <t>CEU4</t>
   </si>
   <si>
     <t>DL124</t>
@@ -160,16 +140,10 @@
     <t>DL404</t>
   </si>
   <si>
-    <t>DL416</t>
-  </si>
-  <si>
     <t>DL426</t>
   </si>
   <si>
     <t>DL438</t>
-  </si>
-  <si>
-    <t>DL490</t>
   </si>
   <si>
     <t>DL511</t>
@@ -197,108 +171,6 @@
   </si>
   <si>
     <t>DL904</t>
-  </si>
-  <si>
-    <t>M2414</t>
-  </si>
-  <si>
-    <t>M2772</t>
-  </si>
-  <si>
-    <t>M3173</t>
-  </si>
-  <si>
-    <t>M3198</t>
-  </si>
-  <si>
-    <t>M3230</t>
-  </si>
-  <si>
-    <t>M3232</t>
-  </si>
-  <si>
-    <t>M3234</t>
-  </si>
-  <si>
-    <t>M3237</t>
-  </si>
-  <si>
-    <t>M3239</t>
-  </si>
-  <si>
-    <t>M3240</t>
-  </si>
-  <si>
-    <t>M3241</t>
-  </si>
-  <si>
-    <t>M3243</t>
-  </si>
-  <si>
-    <t>M3245</t>
-  </si>
-  <si>
-    <t>M3246</t>
-  </si>
-  <si>
-    <t>M3248</t>
-  </si>
-  <si>
-    <t>M3249</t>
-  </si>
-  <si>
-    <t>M3253</t>
-  </si>
-  <si>
-    <t>M3256</t>
-  </si>
-  <si>
-    <t>M3274</t>
-  </si>
-  <si>
-    <t>M3275</t>
-  </si>
-  <si>
-    <t>M3279</t>
-  </si>
-  <si>
-    <t>M3281</t>
-  </si>
-  <si>
-    <t>M3282</t>
-  </si>
-  <si>
-    <t>M3285</t>
-  </si>
-  <si>
-    <t>M3287</t>
-  </si>
-  <si>
-    <t>M3289</t>
-  </si>
-  <si>
-    <t>M3291</t>
-  </si>
-  <si>
-    <t>M3292</t>
-  </si>
-  <si>
-    <t>M3295</t>
-  </si>
-  <si>
-    <t>M3300</t>
-  </si>
-  <si>
-    <t>M3301</t>
-  </si>
-  <si>
-    <t>M3306</t>
-  </si>
-  <si>
-    <t>M3308</t>
-  </si>
-  <si>
-    <t>M3309</t>
   </si>
   <si>
     <t>SI11</t>
@@ -685,3992 +557,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{828972B3-9E96-45A4-86D8-BEE461F973E5}">
-  <dimension ref="A1:C361"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>706</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>737</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>766</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>795</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>797</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>860</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>862</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>880</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>912</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>985</v>
-      </c>
-      <c r="B11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>986</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>987</v>
-      </c>
-      <c r="B13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13">
-        <v>2944</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>991</v>
-      </c>
-      <c r="B14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>993</v>
-      </c>
-      <c r="B15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>999</v>
-      </c>
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16">
-        <v>2944</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>1000</v>
-      </c>
-      <c r="B17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>1001</v>
-      </c>
-      <c r="B18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>1002</v>
-      </c>
-      <c r="B19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>1006</v>
-      </c>
-      <c r="B20" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>1009</v>
-      </c>
-      <c r="B21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>1014</v>
-      </c>
-      <c r="B22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>1031</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>1032</v>
-      </c>
-      <c r="B24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>1094</v>
-      </c>
-      <c r="B25" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>1123</v>
-      </c>
-      <c r="B26" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>1151</v>
-      </c>
-      <c r="B27" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>1195</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>1197</v>
-      </c>
-      <c r="B29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>1198</v>
-      </c>
-      <c r="B30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>1271</v>
-      </c>
-      <c r="B31" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>1272</v>
-      </c>
-      <c r="B32" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>1303</v>
-      </c>
-      <c r="B33" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>1306</v>
-      </c>
-      <c r="B34" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>1308</v>
-      </c>
-      <c r="B35" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>1310</v>
-      </c>
-      <c r="B36" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>1318</v>
-      </c>
-      <c r="B37" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>2376</v>
-      </c>
-      <c r="B38" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>2377</v>
-      </c>
-      <c r="B39" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>2379</v>
-      </c>
-      <c r="B40" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>2402</v>
-      </c>
-      <c r="B41" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>2403</v>
-      </c>
-      <c r="B42" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>2409</v>
-      </c>
-      <c r="B43" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>2416</v>
-      </c>
-      <c r="B44" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>2417</v>
-      </c>
-      <c r="B45" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>2418</v>
-      </c>
-      <c r="B46" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46">
-        <v>2944</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>2420</v>
-      </c>
-      <c r="B47" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>2422</v>
-      </c>
-      <c r="B48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48">
-        <v>2944</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>2425</v>
-      </c>
-      <c r="B49" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49">
-        <v>2944</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>2429</v>
-      </c>
-      <c r="B50" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>2435</v>
-      </c>
-      <c r="B51" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>2437</v>
-      </c>
-      <c r="B52" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>2442</v>
-      </c>
-      <c r="B53" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>2445</v>
-      </c>
-      <c r="B54" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>2446</v>
-      </c>
-      <c r="B55" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>2447</v>
-      </c>
-      <c r="B56" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>2451</v>
-      </c>
-      <c r="B57" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>2454</v>
-      </c>
-      <c r="B58" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>2456</v>
-      </c>
-      <c r="B59" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>2457</v>
-      </c>
-      <c r="B60" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>2459</v>
-      </c>
-      <c r="B61" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>2463</v>
-      </c>
-      <c r="B62" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>2467</v>
-      </c>
-      <c r="B63" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>2472</v>
-      </c>
-      <c r="B64" t="s">
-        <v>2</v>
-      </c>
-      <c r="C64">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>2479</v>
-      </c>
-      <c r="B65" t="s">
-        <v>2</v>
-      </c>
-      <c r="C65">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>2482</v>
-      </c>
-      <c r="B66" t="s">
-        <v>2</v>
-      </c>
-      <c r="C66">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>2483</v>
-      </c>
-      <c r="B67" t="s">
-        <v>2</v>
-      </c>
-      <c r="C67">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>2487</v>
-      </c>
-      <c r="B68" t="s">
-        <v>2</v>
-      </c>
-      <c r="C68">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>2489</v>
-      </c>
-      <c r="B69" t="s">
-        <v>2</v>
-      </c>
-      <c r="C69">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>2491</v>
-      </c>
-      <c r="B70" t="s">
-        <v>2</v>
-      </c>
-      <c r="C70" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>2492</v>
-      </c>
-      <c r="B71" t="s">
-        <v>2</v>
-      </c>
-      <c r="C71">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>2493</v>
-      </c>
-      <c r="B72" t="s">
-        <v>2</v>
-      </c>
-      <c r="C72">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>2495</v>
-      </c>
-      <c r="B73" t="s">
-        <v>2</v>
-      </c>
-      <c r="C73">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>2499</v>
-      </c>
-      <c r="B74" t="s">
-        <v>2</v>
-      </c>
-      <c r="C74">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>2501</v>
-      </c>
-      <c r="B75" t="s">
-        <v>2</v>
-      </c>
-      <c r="C75">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>2541</v>
-      </c>
-      <c r="B76" t="s">
-        <v>2</v>
-      </c>
-      <c r="C76">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>2546</v>
-      </c>
-      <c r="B77" t="s">
-        <v>2</v>
-      </c>
-      <c r="C77">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>2547</v>
-      </c>
-      <c r="B78" t="s">
-        <v>2</v>
-      </c>
-      <c r="C78">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>2550</v>
-      </c>
-      <c r="B79" t="s">
-        <v>2</v>
-      </c>
-      <c r="C79">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>2551</v>
-      </c>
-      <c r="B80" t="s">
-        <v>2</v>
-      </c>
-      <c r="C80">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <v>2554</v>
-      </c>
-      <c r="B81" t="s">
-        <v>2</v>
-      </c>
-      <c r="C81">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <v>2557</v>
-      </c>
-      <c r="B82" t="s">
-        <v>2</v>
-      </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83">
-        <v>2559</v>
-      </c>
-      <c r="B83" t="s">
-        <v>2</v>
-      </c>
-      <c r="C83">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84">
-        <v>2560</v>
-      </c>
-      <c r="B84" t="s">
-        <v>2</v>
-      </c>
-      <c r="C84">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85">
-        <v>2562</v>
-      </c>
-      <c r="B85" t="s">
-        <v>2</v>
-      </c>
-      <c r="C85">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86">
-        <v>2564</v>
-      </c>
-      <c r="B86" t="s">
-        <v>2</v>
-      </c>
-      <c r="C86">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <v>2569</v>
-      </c>
-      <c r="B87" t="s">
-        <v>2</v>
-      </c>
-      <c r="C87">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>2571</v>
-      </c>
-      <c r="B88" t="s">
-        <v>2</v>
-      </c>
-      <c r="C88">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>2576</v>
-      </c>
-      <c r="B89" t="s">
-        <v>2</v>
-      </c>
-      <c r="C89">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>2577</v>
-      </c>
-      <c r="B90" t="s">
-        <v>2</v>
-      </c>
-      <c r="C90">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>2580</v>
-      </c>
-      <c r="B91" t="s">
-        <v>2</v>
-      </c>
-      <c r="C91">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>2581</v>
-      </c>
-      <c r="B92" t="s">
-        <v>2</v>
-      </c>
-      <c r="C92">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>2583</v>
-      </c>
-      <c r="B93" t="s">
-        <v>2</v>
-      </c>
-      <c r="C93">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <v>2585</v>
-      </c>
-      <c r="B94" t="s">
-        <v>2</v>
-      </c>
-      <c r="C94">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <v>2590</v>
-      </c>
-      <c r="B95" t="s">
-        <v>2</v>
-      </c>
-      <c r="C95">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96">
-        <v>2591</v>
-      </c>
-      <c r="B96" t="s">
-        <v>2</v>
-      </c>
-      <c r="C96">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <v>2592</v>
-      </c>
-      <c r="B97" t="s">
-        <v>2</v>
-      </c>
-      <c r="C97">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98">
-        <v>2593</v>
-      </c>
-      <c r="B98" t="s">
-        <v>2</v>
-      </c>
-      <c r="C98">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <v>2594</v>
-      </c>
-      <c r="B99" t="s">
-        <v>2</v>
-      </c>
-      <c r="C99">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100">
-        <v>2595</v>
-      </c>
-      <c r="B100" t="s">
-        <v>2</v>
-      </c>
-      <c r="C100">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <v>2596</v>
-      </c>
-      <c r="B101" t="s">
-        <v>2</v>
-      </c>
-      <c r="C101">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <v>2598</v>
-      </c>
-      <c r="B102" t="s">
-        <v>2</v>
-      </c>
-      <c r="C102">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>2602</v>
-      </c>
-      <c r="B103" t="s">
-        <v>2</v>
-      </c>
-      <c r="C103">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <v>2603</v>
-      </c>
-      <c r="B104" t="s">
-        <v>2</v>
-      </c>
-      <c r="C104">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <v>2606</v>
-      </c>
-      <c r="B105" t="s">
-        <v>2</v>
-      </c>
-      <c r="C105">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>2610</v>
-      </c>
-      <c r="B106" t="s">
-        <v>2</v>
-      </c>
-      <c r="C106">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <v>2621</v>
-      </c>
-      <c r="B107" t="s">
-        <v>2</v>
-      </c>
-      <c r="C107">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108">
-        <v>2622</v>
-      </c>
-      <c r="B108" t="s">
-        <v>2</v>
-      </c>
-      <c r="C108">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109">
-        <v>2624</v>
-      </c>
-      <c r="B109" t="s">
-        <v>2</v>
-      </c>
-      <c r="C109">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110">
-        <v>2625</v>
-      </c>
-      <c r="B110" t="s">
-        <v>2</v>
-      </c>
-      <c r="C110">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <v>2627</v>
-      </c>
-      <c r="B111" t="s">
-        <v>2</v>
-      </c>
-      <c r="C111">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112">
-        <v>2628</v>
-      </c>
-      <c r="B112" t="s">
-        <v>2</v>
-      </c>
-      <c r="C112">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113">
-        <v>2629</v>
-      </c>
-      <c r="B113" t="s">
-        <v>2</v>
-      </c>
-      <c r="C113">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114">
-        <v>2630</v>
-      </c>
-      <c r="B114" t="s">
-        <v>2</v>
-      </c>
-      <c r="C114">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115">
-        <v>2632</v>
-      </c>
-      <c r="B115" t="s">
-        <v>2</v>
-      </c>
-      <c r="C115" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116">
-        <v>2634</v>
-      </c>
-      <c r="B116" t="s">
-        <v>2</v>
-      </c>
-      <c r="C116">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117">
-        <v>2637</v>
-      </c>
-      <c r="B117" t="s">
-        <v>2</v>
-      </c>
-      <c r="C117">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118">
-        <v>2638</v>
-      </c>
-      <c r="B118" t="s">
-        <v>2</v>
-      </c>
-      <c r="C118">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119">
-        <v>2639</v>
-      </c>
-      <c r="B119" t="s">
-        <v>2</v>
-      </c>
-      <c r="C119">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120">
-        <v>2640</v>
-      </c>
-      <c r="B120" t="s">
-        <v>2</v>
-      </c>
-      <c r="C120">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121">
-        <v>2641</v>
-      </c>
-      <c r="B121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C121">
-        <v>2944</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122">
-        <v>2644</v>
-      </c>
-      <c r="B122" t="s">
-        <v>2</v>
-      </c>
-      <c r="C122">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123">
-        <v>2649</v>
-      </c>
-      <c r="B123" t="s">
-        <v>2</v>
-      </c>
-      <c r="C123">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124">
-        <v>2650</v>
-      </c>
-      <c r="B124" t="s">
-        <v>2</v>
-      </c>
-      <c r="C124">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125">
-        <v>2654</v>
-      </c>
-      <c r="B125" t="s">
-        <v>2</v>
-      </c>
-      <c r="C125" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126">
-        <v>2658</v>
-      </c>
-      <c r="B126" t="s">
-        <v>2</v>
-      </c>
-      <c r="C126">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127">
-        <v>2660</v>
-      </c>
-      <c r="B127" t="s">
-        <v>2</v>
-      </c>
-      <c r="C127">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128">
-        <v>2661</v>
-      </c>
-      <c r="B128" t="s">
-        <v>2</v>
-      </c>
-      <c r="C128">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129">
-        <v>2665</v>
-      </c>
-      <c r="B129" t="s">
-        <v>2</v>
-      </c>
-      <c r="C129">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130">
-        <v>2666</v>
-      </c>
-      <c r="B130" t="s">
-        <v>2</v>
-      </c>
-      <c r="C130">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131">
-        <v>2669</v>
-      </c>
-      <c r="B131" t="s">
-        <v>2</v>
-      </c>
-      <c r="C131">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132">
-        <v>2672</v>
-      </c>
-      <c r="B132" t="s">
-        <v>2</v>
-      </c>
-      <c r="C132">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133">
-        <v>2674</v>
-      </c>
-      <c r="B133" t="s">
-        <v>2</v>
-      </c>
-      <c r="C133">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134">
-        <v>2676</v>
-      </c>
-      <c r="B134" t="s">
-        <v>2</v>
-      </c>
-      <c r="C134">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135">
-        <v>2678</v>
-      </c>
-      <c r="B135" t="s">
-        <v>2</v>
-      </c>
-      <c r="C135">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136">
-        <v>2681</v>
-      </c>
-      <c r="B136" t="s">
-        <v>2</v>
-      </c>
-      <c r="C136">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137">
-        <v>2686</v>
-      </c>
-      <c r="B137" t="s">
-        <v>2</v>
-      </c>
-      <c r="C137">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138">
-        <v>2687</v>
-      </c>
-      <c r="B138" t="s">
-        <v>2</v>
-      </c>
-      <c r="C138">
-        <v>8727</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139">
-        <v>2689</v>
-      </c>
-      <c r="B139" t="s">
-        <v>2</v>
-      </c>
-      <c r="C139">
-        <v>8727</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140">
-        <v>2692</v>
-      </c>
-      <c r="B140" t="s">
-        <v>2</v>
-      </c>
-      <c r="C140">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141">
-        <v>2695</v>
-      </c>
-      <c r="B141" t="s">
-        <v>2</v>
-      </c>
-      <c r="C141">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142">
-        <v>2709</v>
-      </c>
-      <c r="B142" t="s">
-        <v>2</v>
-      </c>
-      <c r="C142">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143">
-        <v>2720</v>
-      </c>
-      <c r="B143" t="s">
-        <v>2</v>
-      </c>
-      <c r="C143">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144">
-        <v>2721</v>
-      </c>
-      <c r="B144" t="s">
-        <v>2</v>
-      </c>
-      <c r="C144">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145">
-        <v>2722</v>
-      </c>
-      <c r="B145" t="s">
-        <v>2</v>
-      </c>
-      <c r="C145">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146">
-        <v>2723</v>
-      </c>
-      <c r="B146" t="s">
-        <v>2</v>
-      </c>
-      <c r="C146">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147">
-        <v>2728</v>
-      </c>
-      <c r="B147" t="s">
-        <v>2</v>
-      </c>
-      <c r="C147">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148">
-        <v>2730</v>
-      </c>
-      <c r="B148" t="s">
-        <v>2</v>
-      </c>
-      <c r="C148">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149">
-        <v>2731</v>
-      </c>
-      <c r="B149" t="s">
-        <v>2</v>
-      </c>
-      <c r="C149">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150">
-        <v>2732</v>
-      </c>
-      <c r="B150" t="s">
-        <v>2</v>
-      </c>
-      <c r="C150">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151">
-        <v>2736</v>
-      </c>
-      <c r="B151" t="s">
-        <v>2</v>
-      </c>
-      <c r="C151">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152">
-        <v>2738</v>
-      </c>
-      <c r="B152" t="s">
-        <v>2</v>
-      </c>
-      <c r="C152">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153">
-        <v>2746</v>
-      </c>
-      <c r="B153" t="s">
-        <v>2</v>
-      </c>
-      <c r="C153">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154">
-        <v>2750</v>
-      </c>
-      <c r="B154" t="s">
-        <v>2</v>
-      </c>
-      <c r="C154">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155">
-        <v>2752</v>
-      </c>
-      <c r="B155" t="s">
-        <v>2</v>
-      </c>
-      <c r="C155">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156">
-        <v>2753</v>
-      </c>
-      <c r="B156" t="s">
-        <v>2</v>
-      </c>
-      <c r="C156">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157">
-        <v>2755</v>
-      </c>
-      <c r="B157" t="s">
-        <v>2</v>
-      </c>
-      <c r="C157">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158">
-        <v>2756</v>
-      </c>
-      <c r="B158" t="s">
-        <v>2</v>
-      </c>
-      <c r="C158">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159">
-        <v>2758</v>
-      </c>
-      <c r="B159" t="s">
-        <v>2</v>
-      </c>
-      <c r="C159">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160">
-        <v>2764</v>
-      </c>
-      <c r="B160" t="s">
-        <v>2</v>
-      </c>
-      <c r="C160">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A161">
-        <v>2769</v>
-      </c>
-      <c r="B161" t="s">
-        <v>2</v>
-      </c>
-      <c r="C161">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A162">
-        <v>2774</v>
-      </c>
-      <c r="B162" t="s">
-        <v>2</v>
-      </c>
-      <c r="C162">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A163">
-        <v>2781</v>
-      </c>
-      <c r="B163" t="s">
-        <v>2</v>
-      </c>
-      <c r="C163">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A164">
-        <v>2782</v>
-      </c>
-      <c r="B164" t="s">
-        <v>2</v>
-      </c>
-      <c r="C164">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165">
-        <v>2787</v>
-      </c>
-      <c r="B165" t="s">
-        <v>2</v>
-      </c>
-      <c r="C165">
-        <v>2944</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A166">
-        <v>2792</v>
-      </c>
-      <c r="B166" t="s">
-        <v>2</v>
-      </c>
-      <c r="C166">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A167">
-        <v>2793</v>
-      </c>
-      <c r="B167" t="s">
-        <v>2</v>
-      </c>
-      <c r="C167">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A168">
-        <v>2794</v>
-      </c>
-      <c r="B168" t="s">
-        <v>2</v>
-      </c>
-      <c r="C168">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169">
-        <v>2795</v>
-      </c>
-      <c r="B169" t="s">
-        <v>2</v>
-      </c>
-      <c r="C169">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A170">
-        <v>2813</v>
-      </c>
-      <c r="B170" t="s">
-        <v>2</v>
-      </c>
-      <c r="C170">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171">
-        <v>2815</v>
-      </c>
-      <c r="B171" t="s">
-        <v>2</v>
-      </c>
-      <c r="C171">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172">
-        <v>2822</v>
-      </c>
-      <c r="B172" t="s">
-        <v>2</v>
-      </c>
-      <c r="C172">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A173">
-        <v>2827</v>
-      </c>
-      <c r="B173" t="s">
-        <v>2</v>
-      </c>
-      <c r="C173">
-        <v>2951</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A174">
-        <v>2834</v>
-      </c>
-      <c r="B174" t="s">
-        <v>2</v>
-      </c>
-      <c r="C174">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175">
-        <v>2839</v>
-      </c>
-      <c r="B175" t="s">
-        <v>2</v>
-      </c>
-      <c r="C175">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A176">
-        <v>2840</v>
-      </c>
-      <c r="B176" t="s">
-        <v>2</v>
-      </c>
-      <c r="C176">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A177">
-        <v>2842</v>
-      </c>
-      <c r="B177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C177">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A178">
-        <v>2845</v>
-      </c>
-      <c r="B178" t="s">
-        <v>2</v>
-      </c>
-      <c r="C178">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A179">
-        <v>2846</v>
-      </c>
-      <c r="B179" t="s">
-        <v>2</v>
-      </c>
-      <c r="C179">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A180">
-        <v>2847</v>
-      </c>
-      <c r="B180" t="s">
-        <v>2</v>
-      </c>
-      <c r="C180">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A181">
-        <v>2848</v>
-      </c>
-      <c r="B181" t="s">
-        <v>2</v>
-      </c>
-      <c r="C181">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A182">
-        <v>2852</v>
-      </c>
-      <c r="B182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C182">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A183">
-        <v>2855</v>
-      </c>
-      <c r="B183" t="s">
-        <v>2</v>
-      </c>
-      <c r="C183">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A184">
-        <v>2863</v>
-      </c>
-      <c r="B184" t="s">
-        <v>2</v>
-      </c>
-      <c r="C184">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A185">
-        <v>2866</v>
-      </c>
-      <c r="B185" t="s">
-        <v>2</v>
-      </c>
-      <c r="C185">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A186">
-        <v>2870</v>
-      </c>
-      <c r="B186" t="s">
-        <v>2</v>
-      </c>
-      <c r="C186">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A187">
-        <v>2874</v>
-      </c>
-      <c r="B187" t="s">
-        <v>2</v>
-      </c>
-      <c r="C187">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188">
-        <v>2879</v>
-      </c>
-      <c r="B188" t="s">
-        <v>2</v>
-      </c>
-      <c r="C188">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A189">
-        <v>2881</v>
-      </c>
-      <c r="B189" t="s">
-        <v>2</v>
-      </c>
-      <c r="C189">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A190">
-        <v>2889</v>
-      </c>
-      <c r="B190" t="s">
-        <v>2</v>
-      </c>
-      <c r="C190">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A191">
-        <v>2890</v>
-      </c>
-      <c r="B191" t="s">
-        <v>2</v>
-      </c>
-      <c r="C191">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A192">
-        <v>2893</v>
-      </c>
-      <c r="B192" t="s">
-        <v>2</v>
-      </c>
-      <c r="C192">
-        <v>8727</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193">
-        <v>2895</v>
-      </c>
-      <c r="B193" t="s">
-        <v>2</v>
-      </c>
-      <c r="C193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A194">
-        <v>2897</v>
-      </c>
-      <c r="B194" t="s">
-        <v>2</v>
-      </c>
-      <c r="C194">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195">
-        <v>2899</v>
-      </c>
-      <c r="B195" t="s">
-        <v>2</v>
-      </c>
-      <c r="C195">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A196">
-        <v>2905</v>
-      </c>
-      <c r="B196" t="s">
-        <v>2</v>
-      </c>
-      <c r="C196">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A197">
-        <v>2911</v>
-      </c>
-      <c r="B197" t="s">
-        <v>2</v>
-      </c>
-      <c r="C197">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198">
-        <v>2914</v>
-      </c>
-      <c r="B198" t="s">
-        <v>2</v>
-      </c>
-      <c r="C198">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A199">
-        <v>2919</v>
-      </c>
-      <c r="B199" t="s">
-        <v>2</v>
-      </c>
-      <c r="C199">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A200">
-        <v>2922</v>
-      </c>
-      <c r="B200" t="s">
-        <v>2</v>
-      </c>
-      <c r="C200">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A201">
-        <v>2929</v>
-      </c>
-      <c r="B201" t="s">
-        <v>2</v>
-      </c>
-      <c r="C201">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A202">
-        <v>2942</v>
-      </c>
-      <c r="B202" t="s">
-        <v>2</v>
-      </c>
-      <c r="C202">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A203">
-        <v>2943</v>
-      </c>
-      <c r="B203" t="s">
-        <v>2</v>
-      </c>
-      <c r="C203">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A204">
-        <v>2949</v>
-      </c>
-      <c r="B204" t="s">
-        <v>2</v>
-      </c>
-      <c r="C204">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A205">
-        <v>2951</v>
-      </c>
-      <c r="B205" t="s">
-        <v>2</v>
-      </c>
-      <c r="C205">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A206">
-        <v>2954</v>
-      </c>
-      <c r="B206" t="s">
-        <v>2</v>
-      </c>
-      <c r="C206">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A207">
-        <v>2956</v>
-      </c>
-      <c r="B207" t="s">
-        <v>2</v>
-      </c>
-      <c r="C207">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A208">
-        <v>2958</v>
-      </c>
-      <c r="B208" t="s">
-        <v>2</v>
-      </c>
-      <c r="C208">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A209">
-        <v>2960</v>
-      </c>
-      <c r="B209" t="s">
-        <v>2</v>
-      </c>
-      <c r="C209">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A210">
-        <v>2962</v>
-      </c>
-      <c r="B210" t="s">
-        <v>2</v>
-      </c>
-      <c r="C210">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A211">
-        <v>2963</v>
-      </c>
-      <c r="B211" t="s">
-        <v>2</v>
-      </c>
-      <c r="C211">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A212">
-        <v>2964</v>
-      </c>
-      <c r="B212" t="s">
-        <v>2</v>
-      </c>
-      <c r="C212">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A213">
-        <v>2965</v>
-      </c>
-      <c r="B213" t="s">
-        <v>2</v>
-      </c>
-      <c r="C213">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A214">
-        <v>2973</v>
-      </c>
-      <c r="B214" t="s">
-        <v>2</v>
-      </c>
-      <c r="C214">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A215">
-        <v>2977</v>
-      </c>
-      <c r="B215" t="s">
-        <v>2</v>
-      </c>
-      <c r="C215">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A216">
-        <v>2978</v>
-      </c>
-      <c r="B216" t="s">
-        <v>2</v>
-      </c>
-      <c r="C216">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A217">
-        <v>2983</v>
-      </c>
-      <c r="B217" t="s">
-        <v>2</v>
-      </c>
-      <c r="C217">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A218">
-        <v>2984</v>
-      </c>
-      <c r="B218" t="s">
-        <v>2</v>
-      </c>
-      <c r="C218">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A219">
-        <v>2990</v>
-      </c>
-      <c r="B219" t="s">
-        <v>2</v>
-      </c>
-      <c r="C219">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A220">
-        <v>3005</v>
-      </c>
-      <c r="B220" t="s">
-        <v>2</v>
-      </c>
-      <c r="C220">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A221">
-        <v>3006</v>
-      </c>
-      <c r="B221" t="s">
-        <v>2</v>
-      </c>
-      <c r="C221">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A222">
-        <v>3007</v>
-      </c>
-      <c r="B222" t="s">
-        <v>2</v>
-      </c>
-      <c r="C222">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A223">
-        <v>3011</v>
-      </c>
-      <c r="B223" t="s">
-        <v>2</v>
-      </c>
-      <c r="C223">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A224">
-        <v>3018</v>
-      </c>
-      <c r="B224" t="s">
-        <v>2</v>
-      </c>
-      <c r="C224">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A225">
-        <v>3019</v>
-      </c>
-      <c r="B225" t="s">
-        <v>2</v>
-      </c>
-      <c r="C225">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A226">
-        <v>3020</v>
-      </c>
-      <c r="B226" t="s">
-        <v>2</v>
-      </c>
-      <c r="C226">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A227">
-        <v>3021</v>
-      </c>
-      <c r="B227" t="s">
-        <v>2</v>
-      </c>
-      <c r="C227">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A228">
-        <v>3025</v>
-      </c>
-      <c r="B228" t="s">
-        <v>2</v>
-      </c>
-      <c r="C228">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A229">
-        <v>3026</v>
-      </c>
-      <c r="B229" t="s">
-        <v>2</v>
-      </c>
-      <c r="C229">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A230">
-        <v>3035</v>
-      </c>
-      <c r="B230" t="s">
-        <v>2</v>
-      </c>
-      <c r="C230">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A231">
-        <v>3046</v>
-      </c>
-      <c r="B231" t="s">
-        <v>2</v>
-      </c>
-      <c r="C231">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A232">
-        <v>3050</v>
-      </c>
-      <c r="B232" t="s">
-        <v>2</v>
-      </c>
-      <c r="C232">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A233">
-        <v>3051</v>
-      </c>
-      <c r="B233" t="s">
-        <v>2</v>
-      </c>
-      <c r="C233">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A234">
-        <v>3052</v>
-      </c>
-      <c r="B234" t="s">
-        <v>2</v>
-      </c>
-      <c r="C234">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A235">
-        <v>3053</v>
-      </c>
-      <c r="B235" t="s">
-        <v>2</v>
-      </c>
-      <c r="C235">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A236">
-        <v>3057</v>
-      </c>
-      <c r="B236" t="s">
-        <v>2</v>
-      </c>
-      <c r="C236">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A237">
-        <v>3060</v>
-      </c>
-      <c r="B237" t="s">
-        <v>2</v>
-      </c>
-      <c r="C237">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A238">
-        <v>3062</v>
-      </c>
-      <c r="B238" t="s">
-        <v>2</v>
-      </c>
-      <c r="C238">
-        <v>4132</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A239">
-        <v>3064</v>
-      </c>
-      <c r="B239" t="s">
-        <v>2</v>
-      </c>
-      <c r="C239">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A240">
-        <v>3070</v>
-      </c>
-      <c r="B240" t="s">
-        <v>2</v>
-      </c>
-      <c r="C240">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A241">
-        <v>3074</v>
-      </c>
-      <c r="B241" t="s">
-        <v>2</v>
-      </c>
-      <c r="C241">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A242">
-        <v>3076</v>
-      </c>
-      <c r="B242" t="s">
-        <v>2</v>
-      </c>
-      <c r="C242">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A243">
-        <v>3086</v>
-      </c>
-      <c r="B243" t="s">
-        <v>2</v>
-      </c>
-      <c r="C243">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A244">
-        <v>3099</v>
-      </c>
-      <c r="B244" t="s">
-        <v>2</v>
-      </c>
-      <c r="C244">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A245">
-        <v>3101</v>
-      </c>
-      <c r="B245" t="s">
-        <v>2</v>
-      </c>
-      <c r="C245">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A246">
-        <v>3102</v>
-      </c>
-      <c r="B246" t="s">
-        <v>2</v>
-      </c>
-      <c r="C246">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A247">
-        <v>3103</v>
-      </c>
-      <c r="B247" t="s">
-        <v>2</v>
-      </c>
-      <c r="C247">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A248">
-        <v>3104</v>
-      </c>
-      <c r="B248" t="s">
-        <v>2</v>
-      </c>
-      <c r="C248">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A249">
-        <v>3110</v>
-      </c>
-      <c r="B249" t="s">
-        <v>2</v>
-      </c>
-      <c r="C249">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A250">
-        <v>3113</v>
-      </c>
-      <c r="B250" t="s">
-        <v>2</v>
-      </c>
-      <c r="C250">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A251">
-        <v>3120</v>
-      </c>
-      <c r="B251" t="s">
-        <v>2</v>
-      </c>
-      <c r="C251">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A252">
-        <v>3123</v>
-      </c>
-      <c r="B252" t="s">
-        <v>2</v>
-      </c>
-      <c r="C252">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A253">
-        <v>3126</v>
-      </c>
-      <c r="B253" t="s">
-        <v>2</v>
-      </c>
-      <c r="C253">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A254">
-        <v>3129</v>
-      </c>
-      <c r="B254" t="s">
-        <v>2</v>
-      </c>
-      <c r="C254">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A255">
-        <v>3130</v>
-      </c>
-      <c r="B255" t="s">
-        <v>2</v>
-      </c>
-      <c r="C255">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A256">
-        <v>3135</v>
-      </c>
-      <c r="B256" t="s">
-        <v>2</v>
-      </c>
-      <c r="C256">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A257">
-        <v>3140</v>
-      </c>
-      <c r="B257" t="s">
-        <v>2</v>
-      </c>
-      <c r="C257">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A258">
-        <v>3142</v>
-      </c>
-      <c r="B258" t="s">
-        <v>2</v>
-      </c>
-      <c r="C258">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A259">
-        <v>3145</v>
-      </c>
-      <c r="B259" t="s">
-        <v>2</v>
-      </c>
-      <c r="C259">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A260">
-        <v>3153</v>
-      </c>
-      <c r="B260" t="s">
-        <v>2</v>
-      </c>
-      <c r="C260">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A261">
-        <v>3160</v>
-      </c>
-      <c r="B261" t="s">
-        <v>2</v>
-      </c>
-      <c r="C261">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A262">
-        <v>3161</v>
-      </c>
-      <c r="B262" t="s">
-        <v>2</v>
-      </c>
-      <c r="C262">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A263">
-        <v>3163</v>
-      </c>
-      <c r="B263" t="s">
-        <v>2</v>
-      </c>
-      <c r="C263">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A264">
-        <v>3166</v>
-      </c>
-      <c r="B264" t="s">
-        <v>2</v>
-      </c>
-      <c r="C264">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A265">
-        <v>3171</v>
-      </c>
-      <c r="B265" t="s">
-        <v>2</v>
-      </c>
-      <c r="C265">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A266">
-        <v>3172</v>
-      </c>
-      <c r="B266" t="s">
-        <v>2</v>
-      </c>
-      <c r="C266">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A267">
-        <v>3178</v>
-      </c>
-      <c r="B267" t="s">
-        <v>2</v>
-      </c>
-      <c r="C267" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A268">
-        <v>3184</v>
-      </c>
-      <c r="B268" t="s">
-        <v>2</v>
-      </c>
-      <c r="C268" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A269">
-        <v>3187</v>
-      </c>
-      <c r="B269" t="s">
-        <v>2</v>
-      </c>
-      <c r="C269" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A270">
-        <v>3195</v>
-      </c>
-      <c r="B270" t="s">
-        <v>2</v>
-      </c>
-      <c r="C270" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A271">
-        <v>3202</v>
-      </c>
-      <c r="B271" t="s">
-        <v>2</v>
-      </c>
-      <c r="C271">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A272">
-        <v>3203</v>
-      </c>
-      <c r="B272" t="s">
-        <v>2</v>
-      </c>
-      <c r="C272">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A273">
-        <v>3208</v>
-      </c>
-      <c r="B273" t="s">
-        <v>2</v>
-      </c>
-      <c r="C273">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
-        <v>5</v>
-      </c>
-      <c r="B274" t="s">
-        <v>2</v>
-      </c>
-      <c r="C274">
-        <v>2944</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A275" t="s">
-        <v>6</v>
-      </c>
-      <c r="B275" t="s">
-        <v>2</v>
-      </c>
-      <c r="C275">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A276" t="s">
-        <v>7</v>
-      </c>
-      <c r="B276" t="s">
-        <v>2</v>
-      </c>
-      <c r="C276">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A277" t="s">
-        <v>8</v>
-      </c>
-      <c r="B277" t="s">
-        <v>2</v>
-      </c>
-      <c r="C277">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A278" t="s">
-        <v>9</v>
-      </c>
-      <c r="B278" t="s">
-        <v>2</v>
-      </c>
-      <c r="C278">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A279" t="s">
-        <v>10</v>
-      </c>
-      <c r="B279" t="s">
-        <v>2</v>
-      </c>
-      <c r="C279">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A280" t="s">
-        <v>11</v>
-      </c>
-      <c r="B280" t="s">
-        <v>2</v>
-      </c>
-      <c r="C280">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
-        <v>12</v>
-      </c>
-      <c r="B281" t="s">
-        <v>2</v>
-      </c>
-      <c r="C281">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
-        <v>13</v>
-      </c>
-      <c r="B282" t="s">
-        <v>2</v>
-      </c>
-      <c r="C282">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A283" t="s">
-        <v>14</v>
-      </c>
-      <c r="B283" t="s">
-        <v>2</v>
-      </c>
-      <c r="C283">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A284" t="s">
-        <v>15</v>
-      </c>
-      <c r="B284" t="s">
-        <v>2</v>
-      </c>
-      <c r="C284">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A285" t="s">
-        <v>16</v>
-      </c>
-      <c r="B285" t="s">
-        <v>2</v>
-      </c>
-      <c r="C285">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A286" t="s">
-        <v>17</v>
-      </c>
-      <c r="B286" t="s">
-        <v>2</v>
-      </c>
-      <c r="C286">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A287" t="s">
-        <v>18</v>
-      </c>
-      <c r="B287" t="s">
-        <v>2</v>
-      </c>
-      <c r="C287">
-        <v>3759</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A288" t="s">
-        <v>19</v>
-      </c>
-      <c r="B288" t="s">
-        <v>2</v>
-      </c>
-      <c r="C288">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A289" t="s">
-        <v>20</v>
-      </c>
-      <c r="B289" t="s">
-        <v>2</v>
-      </c>
-      <c r="C289" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A290" t="s">
-        <v>21</v>
-      </c>
-      <c r="B290" t="s">
-        <v>2</v>
-      </c>
-      <c r="C290">
-        <v>2780</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A291" t="s">
-        <v>22</v>
-      </c>
-      <c r="B291" t="s">
-        <v>2</v>
-      </c>
-      <c r="C291">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
-        <v>23</v>
-      </c>
-      <c r="B292" t="s">
-        <v>2</v>
-      </c>
-      <c r="C292">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
-        <v>24</v>
-      </c>
-      <c r="B293" t="s">
-        <v>2</v>
-      </c>
-      <c r="C293">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>25</v>
-      </c>
-      <c r="B294" t="s">
-        <v>2</v>
-      </c>
-      <c r="C294">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
-        <v>26</v>
-      </c>
-      <c r="B295" t="s">
-        <v>2</v>
-      </c>
-      <c r="C295">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A296" t="s">
-        <v>27</v>
-      </c>
-      <c r="B296" t="s">
-        <v>2</v>
-      </c>
-      <c r="C296">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
-        <v>28</v>
-      </c>
-      <c r="B297" t="s">
-        <v>2</v>
-      </c>
-      <c r="C297">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
-        <v>29</v>
-      </c>
-      <c r="B298" t="s">
-        <v>2</v>
-      </c>
-      <c r="C298" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A299" t="s">
-        <v>30</v>
-      </c>
-      <c r="B299" t="s">
-        <v>2</v>
-      </c>
-      <c r="C299">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A300" t="s">
-        <v>31</v>
-      </c>
-      <c r="B300" t="s">
-        <v>2</v>
-      </c>
-      <c r="C300">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A301" t="s">
-        <v>32</v>
-      </c>
-      <c r="B301" t="s">
-        <v>2</v>
-      </c>
-      <c r="C301">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
-        <v>33</v>
-      </c>
-      <c r="B302" t="s">
-        <v>2</v>
-      </c>
-      <c r="C302" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A303" t="s">
-        <v>34</v>
-      </c>
-      <c r="B303" t="s">
-        <v>2</v>
-      </c>
-      <c r="C303">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
-        <v>35</v>
-      </c>
-      <c r="B304" t="s">
-        <v>2</v>
-      </c>
-      <c r="C304">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A305" t="s">
-        <v>36</v>
-      </c>
-      <c r="B305" t="s">
-        <v>2</v>
-      </c>
-      <c r="C305">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A306" t="s">
-        <v>37</v>
-      </c>
-      <c r="B306" t="s">
-        <v>2</v>
-      </c>
-      <c r="C306">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A307" t="s">
-        <v>38</v>
-      </c>
-      <c r="B307" t="s">
-        <v>2</v>
-      </c>
-      <c r="C307">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A308" t="s">
-        <v>39</v>
-      </c>
-      <c r="B308" t="s">
-        <v>2</v>
-      </c>
-      <c r="C308">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A309" t="s">
-        <v>40</v>
-      </c>
-      <c r="B309" t="s">
-        <v>2</v>
-      </c>
-      <c r="C309">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A310" t="s">
-        <v>41</v>
-      </c>
-      <c r="B310" t="s">
-        <v>2</v>
-      </c>
-      <c r="C310">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A311" t="s">
-        <v>42</v>
-      </c>
-      <c r="B311" t="s">
-        <v>2</v>
-      </c>
-      <c r="C311">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A312" t="s">
-        <v>43</v>
-      </c>
-      <c r="B312" t="s">
-        <v>2</v>
-      </c>
-      <c r="C312">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A313" t="s">
-        <v>44</v>
-      </c>
-      <c r="B313" t="s">
-        <v>2</v>
-      </c>
-      <c r="C313">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A314" t="s">
-        <v>45</v>
-      </c>
-      <c r="B314" t="s">
-        <v>2</v>
-      </c>
-      <c r="C314">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A315" t="s">
-        <v>46</v>
-      </c>
-      <c r="B315" t="s">
-        <v>2</v>
-      </c>
-      <c r="C315">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A316" t="s">
-        <v>47</v>
-      </c>
-      <c r="B316" t="s">
-        <v>2</v>
-      </c>
-      <c r="C316">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A317" t="s">
-        <v>48</v>
-      </c>
-      <c r="B317" t="s">
-        <v>2</v>
-      </c>
-      <c r="C317">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A318" t="s">
-        <v>49</v>
-      </c>
-      <c r="B318" t="s">
-        <v>2</v>
-      </c>
-      <c r="C318">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A319" t="s">
-        <v>50</v>
-      </c>
-      <c r="B319" t="s">
-        <v>2</v>
-      </c>
-      <c r="C319">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A320" t="s">
-        <v>51</v>
-      </c>
-      <c r="B320" t="s">
-        <v>2</v>
-      </c>
-      <c r="C320">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A321" t="s">
-        <v>52</v>
-      </c>
-      <c r="B321" t="s">
-        <v>2</v>
-      </c>
-      <c r="C321">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A322" t="s">
-        <v>53</v>
-      </c>
-      <c r="B322" t="s">
-        <v>2</v>
-      </c>
-      <c r="C322">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A323" t="s">
-        <v>54</v>
-      </c>
-      <c r="B323" t="s">
-        <v>2</v>
-      </c>
-      <c r="C323">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A324" t="s">
-        <v>55</v>
-      </c>
-      <c r="B324" t="s">
-        <v>2</v>
-      </c>
-      <c r="C324" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A325" t="s">
-        <v>56</v>
-      </c>
-      <c r="B325" t="s">
-        <v>2</v>
-      </c>
-      <c r="C325">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A326" t="s">
-        <v>57</v>
-      </c>
-      <c r="B326" t="s">
-        <v>2</v>
-      </c>
-      <c r="C326">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A327" t="s">
-        <v>58</v>
-      </c>
-      <c r="B327" t="s">
-        <v>2</v>
-      </c>
-      <c r="C327">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A328" t="s">
-        <v>59</v>
-      </c>
-      <c r="B328" t="s">
-        <v>2</v>
-      </c>
-      <c r="C328">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A329" t="s">
-        <v>60</v>
-      </c>
-      <c r="B329" t="s">
-        <v>2</v>
-      </c>
-      <c r="C329">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A330" t="s">
-        <v>61</v>
-      </c>
-      <c r="B330" t="s">
-        <v>2</v>
-      </c>
-      <c r="C330">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A331" t="s">
-        <v>62</v>
-      </c>
-      <c r="B331" t="s">
-        <v>2</v>
-      </c>
-      <c r="C331">
-        <v>2944</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A332" t="s">
-        <v>63</v>
-      </c>
-      <c r="B332" t="s">
-        <v>2</v>
-      </c>
-      <c r="C332">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A333" t="s">
-        <v>64</v>
-      </c>
-      <c r="B333" t="s">
-        <v>2</v>
-      </c>
-      <c r="C333">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A334" t="s">
-        <v>65</v>
-      </c>
-      <c r="B334" t="s">
-        <v>2</v>
-      </c>
-      <c r="C334">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A335" t="s">
-        <v>66</v>
-      </c>
-      <c r="B335" t="s">
-        <v>2</v>
-      </c>
-      <c r="C335">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A336" t="s">
-        <v>67</v>
-      </c>
-      <c r="B336" t="s">
-        <v>2</v>
-      </c>
-      <c r="C336">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A337" t="s">
-        <v>68</v>
-      </c>
-      <c r="B337" t="s">
-        <v>2</v>
-      </c>
-      <c r="C337">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A338" t="s">
-        <v>69</v>
-      </c>
-      <c r="B338" t="s">
-        <v>2</v>
-      </c>
-      <c r="C338">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A339" t="s">
-        <v>70</v>
-      </c>
-      <c r="B339" t="s">
-        <v>2</v>
-      </c>
-      <c r="C339">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A340" t="s">
-        <v>71</v>
-      </c>
-      <c r="B340" t="s">
-        <v>2</v>
-      </c>
-      <c r="C340">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A341" t="s">
-        <v>72</v>
-      </c>
-      <c r="B341" t="s">
-        <v>2</v>
-      </c>
-      <c r="C341">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A342" t="s">
-        <v>73</v>
-      </c>
-      <c r="B342" t="s">
-        <v>2</v>
-      </c>
-      <c r="C342">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A343" t="s">
-        <v>74</v>
-      </c>
-      <c r="B343" t="s">
-        <v>2</v>
-      </c>
-      <c r="C343">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A344" t="s">
-        <v>75</v>
-      </c>
-      <c r="B344" t="s">
-        <v>2</v>
-      </c>
-      <c r="C344">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A345" t="s">
-        <v>76</v>
-      </c>
-      <c r="B345" t="s">
-        <v>2</v>
-      </c>
-      <c r="C345">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A346" t="s">
-        <v>77</v>
-      </c>
-      <c r="B346" t="s">
-        <v>2</v>
-      </c>
-      <c r="C346">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A347" t="s">
-        <v>78</v>
-      </c>
-      <c r="B347" t="s">
-        <v>2</v>
-      </c>
-      <c r="C347">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A348" t="s">
-        <v>79</v>
-      </c>
-      <c r="B348" t="s">
-        <v>2</v>
-      </c>
-      <c r="C348">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A349" t="s">
-        <v>80</v>
-      </c>
-      <c r="B349" t="s">
-        <v>2</v>
-      </c>
-      <c r="C349">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A350" t="s">
-        <v>81</v>
-      </c>
-      <c r="B350" t="s">
-        <v>2</v>
-      </c>
-      <c r="C350">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A351" t="s">
-        <v>82</v>
-      </c>
-      <c r="B351" t="s">
-        <v>2</v>
-      </c>
-      <c r="C351">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A352" t="s">
-        <v>83</v>
-      </c>
-      <c r="B352" t="s">
-        <v>2</v>
-      </c>
-      <c r="C352">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A353" t="s">
-        <v>84</v>
-      </c>
-      <c r="B353" t="s">
-        <v>2</v>
-      </c>
-      <c r="C353">
-        <v>3764</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A354" t="s">
-        <v>85</v>
-      </c>
-      <c r="B354" t="s">
-        <v>2</v>
-      </c>
-      <c r="C354">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A355" t="s">
-        <v>86</v>
-      </c>
-      <c r="B355" t="s">
-        <v>2</v>
-      </c>
-      <c r="C355">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A356" t="s">
-        <v>87</v>
-      </c>
-      <c r="B356" t="s">
-        <v>2</v>
-      </c>
-      <c r="C356">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A357" t="s">
-        <v>88</v>
-      </c>
-      <c r="B357" t="s">
-        <v>2</v>
-      </c>
-      <c r="C357">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A358" t="s">
-        <v>89</v>
-      </c>
-      <c r="B358" t="s">
-        <v>2</v>
-      </c>
-      <c r="C358">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A359" t="s">
-        <v>90</v>
-      </c>
-      <c r="B359" t="s">
-        <v>2</v>
-      </c>
-      <c r="C359">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A360" t="s">
-        <v>91</v>
-      </c>
-      <c r="B360" t="s">
-        <v>2</v>
-      </c>
-      <c r="C360">
-        <v>2855</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A361" t="s">
-        <v>92</v>
-      </c>
-      <c r="B361" t="s">
-        <v>2</v>
-      </c>
-      <c r="C361">
-        <v>2855</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{828972B3-9E96-45A4-86D8-BEE461F973E5}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C361">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CB510BA-4C87-4FE4-889B-5CA8321E6D04}">
   <dimension ref="A1:D359"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4682,16 +568,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -4705,7 +591,7 @@
         <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -4719,7 +605,7 @@
         <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -4733,7 +619,7 @@
         <v>3759</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -4747,7 +633,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -4761,7 +647,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -4775,7 +661,7 @@
         <v>3764</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -4789,7 +675,7 @@
         <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -4803,7 +689,7 @@
         <v>3764</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -4817,7 +703,7 @@
         <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -4831,7 +717,7 @@
         <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -4845,7 +731,7 @@
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -4859,7 +745,7 @@
         <v>2855</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -4873,7 +759,7 @@
         <v>3764</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -4887,7 +773,7 @@
         <v>3764</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -4901,7 +787,7 @@
         <v>2855</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -4915,7 +801,7 @@
         <v>146</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -4929,7 +815,7 @@
         <v>2944</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -4943,7 +829,7 @@
         <v>2855</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -4957,7 +843,7 @@
         <v>2855</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -4971,7 +857,7 @@
         <v>2944</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -4985,7 +871,7 @@
         <v>2855</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -4999,7 +885,7 @@
         <v>2855</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -5013,7 +899,7 @@
         <v>2855</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -5027,7 +913,7 @@
         <v>398</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -5041,7 +927,7 @@
         <v>2855</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -5055,7 +941,7 @@
         <v>2855</v>
       </c>
       <c r="D27" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -5069,7 +955,7 @@
         <v>146</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -5083,7 +969,7 @@
         <v>398</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -5097,7 +983,7 @@
         <v>3764</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -5111,7 +997,7 @@
         <v>3764</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -5125,7 +1011,7 @@
         <v>3764</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -5139,7 +1025,7 @@
         <v>2855</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -5153,7 +1039,7 @@
         <v>3764</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -5167,7 +1053,7 @@
         <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -5181,7 +1067,7 @@
         <v>1945</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -5195,7 +1081,7 @@
         <v>1945</v>
       </c>
       <c r="D37" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -5209,7 +1095,7 @@
         <v>2855</v>
       </c>
       <c r="D38" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -5223,7 +1109,7 @@
         <v>398</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -5237,7 +1123,7 @@
         <v>398</v>
       </c>
       <c r="D40" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -5251,7 +1137,7 @@
         <v>398</v>
       </c>
       <c r="D41" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -5265,7 +1151,7 @@
         <v>2855</v>
       </c>
       <c r="D42" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -5279,7 +1165,7 @@
         <v>3764</v>
       </c>
       <c r="D43" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -5293,7 +1179,7 @@
         <v>3764</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -5307,7 +1193,7 @@
         <v>3764</v>
       </c>
       <c r="D45" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -5321,7 +1207,7 @@
         <v>3764</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -5335,7 +1221,7 @@
         <v>3764</v>
       </c>
       <c r="D47" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -5349,7 +1235,7 @@
         <v>3764</v>
       </c>
       <c r="D48" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -5363,7 +1249,7 @@
         <v>398</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -5377,7 +1263,7 @@
         <v>3764</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -5391,7 +1277,7 @@
         <v>3764</v>
       </c>
       <c r="D51" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -5405,7 +1291,7 @@
         <v>2944</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -5419,7 +1305,7 @@
         <v>3764</v>
       </c>
       <c r="D53" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -5433,7 +1319,7 @@
         <v>2944</v>
       </c>
       <c r="D54" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -5447,7 +1333,7 @@
         <v>2944</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -5461,7 +1347,7 @@
         <v>2855</v>
       </c>
       <c r="D56" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -5475,7 +1361,7 @@
         <v>3764</v>
       </c>
       <c r="D57" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -5489,7 +1375,7 @@
         <v>3764</v>
       </c>
       <c r="D58" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -5503,7 +1389,7 @@
         <v>3764</v>
       </c>
       <c r="D59" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -5517,7 +1403,7 @@
         <v>121</v>
       </c>
       <c r="D60" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -5531,7 +1417,7 @@
         <v>3764</v>
       </c>
       <c r="D61" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -5545,7 +1431,7 @@
         <v>2855</v>
       </c>
       <c r="D62" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -5559,7 +1445,7 @@
         <v>2855</v>
       </c>
       <c r="D63" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -5573,7 +1459,7 @@
         <v>3764</v>
       </c>
       <c r="D64" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -5587,7 +1473,7 @@
         <v>121</v>
       </c>
       <c r="D65" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -5601,7 +1487,7 @@
         <v>2855</v>
       </c>
       <c r="D66" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -5615,7 +1501,7 @@
         <v>121</v>
       </c>
       <c r="D67" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -5629,7 +1515,7 @@
         <v>121</v>
       </c>
       <c r="D68" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -5643,7 +1529,7 @@
         <v>3764</v>
       </c>
       <c r="D69" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -5657,7 +1543,7 @@
         <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -5671,7 +1557,7 @@
         <v>3764</v>
       </c>
       <c r="D71" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -5685,7 +1571,7 @@
         <v>121</v>
       </c>
       <c r="D72" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -5699,7 +1585,7 @@
         <v>96</v>
       </c>
       <c r="D73" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -5713,7 +1599,7 @@
         <v>3764</v>
       </c>
       <c r="D74" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -5727,7 +1613,7 @@
         <v>3764</v>
       </c>
       <c r="D75" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -5738,10 +1624,10 @@
         <v>2021</v>
       </c>
       <c r="C76" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -5755,7 +1641,7 @@
         <v>121</v>
       </c>
       <c r="D77" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -5769,7 +1655,7 @@
         <v>2855</v>
       </c>
       <c r="D78" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -5783,7 +1669,7 @@
         <v>2855</v>
       </c>
       <c r="D79" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -5797,7 +1683,7 @@
         <v>121</v>
       </c>
       <c r="D80" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -5811,7 +1697,7 @@
         <v>3764</v>
       </c>
       <c r="D81" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -5825,7 +1711,7 @@
         <v>121</v>
       </c>
       <c r="D82" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -5839,7 +1725,7 @@
         <v>121</v>
       </c>
       <c r="D83" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -5853,7 +1739,7 @@
         <v>3764</v>
       </c>
       <c r="D84" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -5867,7 +1753,7 @@
         <v>121</v>
       </c>
       <c r="D85" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -5881,7 +1767,7 @@
         <v>121</v>
       </c>
       <c r="D86" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -5895,7 +1781,7 @@
         <v>2855</v>
       </c>
       <c r="D87" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -5909,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -5923,7 +1809,7 @@
         <v>3764</v>
       </c>
       <c r="D89" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -5937,7 +1823,7 @@
         <v>121</v>
       </c>
       <c r="D90" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -5951,7 +1837,7 @@
         <v>121</v>
       </c>
       <c r="D91" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -5965,7 +1851,7 @@
         <v>121</v>
       </c>
       <c r="D92" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -5979,7 +1865,7 @@
         <v>2855</v>
       </c>
       <c r="D93" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -5993,7 +1879,7 @@
         <v>96</v>
       </c>
       <c r="D94" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -6007,7 +1893,7 @@
         <v>3764</v>
       </c>
       <c r="D95" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -6021,7 +1907,7 @@
         <v>2855</v>
       </c>
       <c r="D96" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -6035,7 +1921,7 @@
         <v>2855</v>
       </c>
       <c r="D97" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -6049,7 +1935,7 @@
         <v>2855</v>
       </c>
       <c r="D98" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -6063,7 +1949,7 @@
         <v>2855</v>
       </c>
       <c r="D99" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -6077,7 +1963,7 @@
         <v>2855</v>
       </c>
       <c r="D100" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -6091,7 +1977,7 @@
         <v>121</v>
       </c>
       <c r="D101" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -6105,7 +1991,7 @@
         <v>121</v>
       </c>
       <c r="D102" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -6119,7 +2005,7 @@
         <v>121</v>
       </c>
       <c r="D103" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -6133,7 +2019,7 @@
         <v>121</v>
       </c>
       <c r="D104" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -6147,7 +2033,7 @@
         <v>3764</v>
       </c>
       <c r="D105" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -6161,7 +2047,7 @@
         <v>2855</v>
       </c>
       <c r="D106" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -6175,7 +2061,7 @@
         <v>121</v>
       </c>
       <c r="D107" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -6189,7 +2075,7 @@
         <v>398</v>
       </c>
       <c r="D108" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -6203,7 +2089,7 @@
         <v>3764</v>
       </c>
       <c r="D109" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -6217,7 +2103,7 @@
         <v>398</v>
       </c>
       <c r="D110" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -6231,7 +2117,7 @@
         <v>121</v>
       </c>
       <c r="D111" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -6245,7 +2131,7 @@
         <v>3764</v>
       </c>
       <c r="D112" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -6259,7 +2145,7 @@
         <v>121</v>
       </c>
       <c r="D113" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -6273,7 +2159,7 @@
         <v>96</v>
       </c>
       <c r="D114" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -6287,7 +2173,7 @@
         <v>398</v>
       </c>
       <c r="D115" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -6301,7 +2187,7 @@
         <v>121</v>
       </c>
       <c r="D116" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -6315,7 +2201,7 @@
         <v>96</v>
       </c>
       <c r="D117" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -6329,7 +2215,7 @@
         <v>2855</v>
       </c>
       <c r="D118" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -6343,7 +2229,7 @@
         <v>2855</v>
       </c>
       <c r="D119" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -6357,7 +2243,7 @@
         <v>2855</v>
       </c>
       <c r="D120" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -6368,10 +2254,10 @@
         <v>2022</v>
       </c>
       <c r="C121" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -6385,7 +2271,7 @@
         <v>121</v>
       </c>
       <c r="D122" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -6399,7 +2285,7 @@
         <v>2855</v>
       </c>
       <c r="D123" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -6413,7 +2299,7 @@
         <v>121</v>
       </c>
       <c r="D124" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -6427,7 +2313,7 @@
         <v>121</v>
       </c>
       <c r="D125" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -6441,7 +2327,7 @@
         <v>3764</v>
       </c>
       <c r="D126" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -6455,7 +2341,7 @@
         <v>2944</v>
       </c>
       <c r="D127" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -6469,7 +2355,7 @@
         <v>121</v>
       </c>
       <c r="D128" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -6483,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="D129" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -6497,7 +2383,7 @@
         <v>2855</v>
       </c>
       <c r="D130" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
@@ -6511,7 +2397,7 @@
         <v>2855</v>
       </c>
       <c r="D131" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
@@ -6525,7 +2411,7 @@
         <v>2855</v>
       </c>
       <c r="D132" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -6539,7 +2425,7 @@
         <v>2855</v>
       </c>
       <c r="D133" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
@@ -6553,7 +2439,7 @@
         <v>407</v>
       </c>
       <c r="D134" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
@@ -6567,7 +2453,7 @@
         <v>2855</v>
       </c>
       <c r="D135" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -6581,7 +2467,7 @@
         <v>3764</v>
       </c>
       <c r="D136" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
@@ -6595,7 +2481,7 @@
         <v>3764</v>
       </c>
       <c r="D137" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -6609,7 +2495,7 @@
         <v>3764</v>
       </c>
       <c r="D138" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -6623,7 +2509,7 @@
         <v>398</v>
       </c>
       <c r="D139" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -6637,7 +2523,7 @@
         <v>3764</v>
       </c>
       <c r="D140" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -6651,7 +2537,7 @@
         <v>3764</v>
       </c>
       <c r="D141" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
@@ -6665,7 +2551,7 @@
         <v>121</v>
       </c>
       <c r="D142" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
@@ -6679,7 +2565,7 @@
         <v>8727</v>
       </c>
       <c r="D143" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
@@ -6693,7 +2579,7 @@
         <v>8727</v>
       </c>
       <c r="D144" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
@@ -6707,7 +2593,7 @@
         <v>3764</v>
       </c>
       <c r="D145" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -6721,7 +2607,7 @@
         <v>2855</v>
       </c>
       <c r="D146" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -6735,7 +2621,7 @@
         <v>2855</v>
       </c>
       <c r="D147" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
@@ -6749,7 +2635,7 @@
         <v>121</v>
       </c>
       <c r="D148" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
@@ -6763,7 +2649,7 @@
         <v>121</v>
       </c>
       <c r="D149" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
@@ -6777,7 +2663,7 @@
         <v>2855</v>
       </c>
       <c r="D150" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
@@ -6791,7 +2677,7 @@
         <v>121</v>
       </c>
       <c r="D151" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
@@ -6805,7 +2691,7 @@
         <v>2855</v>
       </c>
       <c r="D152" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
@@ -6819,7 +2705,7 @@
         <v>45</v>
       </c>
       <c r="D153" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
@@ -6833,7 +2719,7 @@
         <v>96</v>
       </c>
       <c r="D154" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
@@ -6847,7 +2733,7 @@
         <v>121</v>
       </c>
       <c r="D155" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
@@ -6861,7 +2747,7 @@
         <v>3764</v>
       </c>
       <c r="D156" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
@@ -6875,7 +2761,7 @@
         <v>121</v>
       </c>
       <c r="D157" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
@@ -6889,7 +2775,7 @@
         <v>3764</v>
       </c>
       <c r="D158" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
@@ -6903,7 +2789,7 @@
         <v>3764</v>
       </c>
       <c r="D159" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
@@ -6917,7 +2803,7 @@
         <v>3764</v>
       </c>
       <c r="D160" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
@@ -6931,7 +2817,7 @@
         <v>121</v>
       </c>
       <c r="D161" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
@@ -6945,7 +2831,7 @@
         <v>398</v>
       </c>
       <c r="D162" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
@@ -6959,7 +2845,7 @@
         <v>121</v>
       </c>
       <c r="D163" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
@@ -6973,7 +2859,7 @@
         <v>2855</v>
       </c>
       <c r="D164" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
@@ -6987,7 +2873,7 @@
         <v>2855</v>
       </c>
       <c r="D165" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
@@ -7001,7 +2887,7 @@
         <v>3764</v>
       </c>
       <c r="D166" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
@@ -7015,7 +2901,7 @@
         <v>146</v>
       </c>
       <c r="D167" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
@@ -7029,7 +2915,7 @@
         <v>121</v>
       </c>
       <c r="D168" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
@@ -7043,7 +2929,7 @@
         <v>3764</v>
       </c>
       <c r="D169" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
@@ -7057,7 +2943,7 @@
         <v>2944</v>
       </c>
       <c r="D170" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
@@ -7071,7 +2957,7 @@
         <v>3764</v>
       </c>
       <c r="D171" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
@@ -7085,7 +2971,7 @@
         <v>3764</v>
       </c>
       <c r="D172" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
@@ -7099,7 +2985,7 @@
         <v>3764</v>
       </c>
       <c r="D173" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
@@ -7113,7 +2999,7 @@
         <v>96</v>
       </c>
       <c r="D174" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
@@ -7127,7 +3013,7 @@
         <v>3764</v>
       </c>
       <c r="D175" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
@@ -7141,7 +3027,7 @@
         <v>3764</v>
       </c>
       <c r="D176" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
@@ -7155,7 +3041,7 @@
         <v>398</v>
       </c>
       <c r="D177" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
@@ -7169,7 +3055,7 @@
         <v>2951</v>
       </c>
       <c r="D178" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
@@ -7183,7 +3069,7 @@
         <v>121</v>
       </c>
       <c r="D179" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
@@ -7197,7 +3083,7 @@
         <v>3764</v>
       </c>
       <c r="D180" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
@@ -7211,7 +3097,7 @@
         <v>398</v>
       </c>
       <c r="D181" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
@@ -7225,7 +3111,7 @@
         <v>2855</v>
       </c>
       <c r="D182" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
@@ -7239,7 +3125,7 @@
         <v>121</v>
       </c>
       <c r="D183" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
@@ -7253,7 +3139,7 @@
         <v>121</v>
       </c>
       <c r="D184" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
@@ -7267,7 +3153,7 @@
         <v>121</v>
       </c>
       <c r="D185" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
@@ -7281,7 +3167,7 @@
         <v>121</v>
       </c>
       <c r="D186" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
@@ -7295,7 +3181,7 @@
         <v>2855</v>
       </c>
       <c r="D187" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
@@ -7309,7 +3195,7 @@
         <v>121</v>
       </c>
       <c r="D188" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
@@ -7323,7 +3209,7 @@
         <v>96</v>
       </c>
       <c r="D189" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
@@ -7337,7 +3223,7 @@
         <v>146</v>
       </c>
       <c r="D190" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
@@ -7351,7 +3237,7 @@
         <v>2855</v>
       </c>
       <c r="D191" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
@@ -7365,7 +3251,7 @@
         <v>2855</v>
       </c>
       <c r="D192" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
@@ -7379,7 +3265,7 @@
         <v>3764</v>
       </c>
       <c r="D193" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
@@ -7393,7 +3279,7 @@
         <v>3764</v>
       </c>
       <c r="D194" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
@@ -7407,7 +3293,7 @@
         <v>3764</v>
       </c>
       <c r="D195" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
@@ -7421,7 +3307,7 @@
         <v>2855</v>
       </c>
       <c r="D196" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
@@ -7435,7 +3321,7 @@
         <v>8727</v>
       </c>
       <c r="D197" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
@@ -7449,7 +3335,7 @@
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
@@ -7463,7 +3349,7 @@
         <v>121</v>
       </c>
       <c r="D199" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
@@ -7477,7 +3363,7 @@
         <v>121</v>
       </c>
       <c r="D200" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
@@ -7491,7 +3377,7 @@
         <v>121</v>
       </c>
       <c r="D201" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
@@ -7505,7 +3391,7 @@
         <v>121</v>
       </c>
       <c r="D202" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
@@ -7519,7 +3405,7 @@
         <v>121</v>
       </c>
       <c r="D203" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
@@ -7533,7 +3419,7 @@
         <v>96</v>
       </c>
       <c r="D204" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
@@ -7547,7 +3433,7 @@
         <v>398</v>
       </c>
       <c r="D205" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
@@ -7561,7 +3447,7 @@
         <v>121</v>
       </c>
       <c r="D206" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
@@ -7575,7 +3461,7 @@
         <v>146</v>
       </c>
       <c r="D207" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
@@ -7589,7 +3475,7 @@
         <v>2855</v>
       </c>
       <c r="D208" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
@@ -7603,7 +3489,7 @@
         <v>146</v>
       </c>
       <c r="D209" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
@@ -7617,7 +3503,7 @@
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
@@ -7631,7 +3517,7 @@
         <v>121</v>
       </c>
       <c r="D211" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
@@ -7645,7 +3531,7 @@
         <v>121</v>
       </c>
       <c r="D212" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
@@ -7659,7 +3545,7 @@
         <v>3764</v>
       </c>
       <c r="D213" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
@@ -7673,7 +3559,7 @@
         <v>3764</v>
       </c>
       <c r="D214" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
@@ -7687,7 +3573,7 @@
         <v>96</v>
       </c>
       <c r="D215" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
@@ -7701,7 +3587,7 @@
         <v>121</v>
       </c>
       <c r="D216" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
@@ -7715,7 +3601,7 @@
         <v>121</v>
       </c>
       <c r="D217" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
@@ -7729,7 +3615,7 @@
         <v>121</v>
       </c>
       <c r="D218" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
@@ -7743,7 +3629,7 @@
         <v>3764</v>
       </c>
       <c r="D219" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
@@ -7757,7 +3643,7 @@
         <v>2855</v>
       </c>
       <c r="D220" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
@@ -7771,7 +3657,7 @@
         <v>121</v>
       </c>
       <c r="D221" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
@@ -7785,7 +3671,7 @@
         <v>3764</v>
       </c>
       <c r="D222" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
@@ -7799,7 +3685,7 @@
         <v>3764</v>
       </c>
       <c r="D223" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
@@ -7813,7 +3699,7 @@
         <v>3764</v>
       </c>
       <c r="D224" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
@@ -7827,7 +3713,7 @@
         <v>3764</v>
       </c>
       <c r="D225" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
@@ -7841,7 +3727,7 @@
         <v>3764</v>
       </c>
       <c r="D226" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
@@ -7855,7 +3741,7 @@
         <v>2855</v>
       </c>
       <c r="D227" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
@@ -7869,7 +3755,7 @@
         <v>2855</v>
       </c>
       <c r="D228" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
@@ -7883,7 +3769,7 @@
         <v>3764</v>
       </c>
       <c r="D229" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
@@ -7897,7 +3783,7 @@
         <v>3764</v>
       </c>
       <c r="D230" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
@@ -7911,7 +3797,7 @@
         <v>96</v>
       </c>
       <c r="D231" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
@@ -7925,7 +3811,7 @@
         <v>3764</v>
       </c>
       <c r="D232" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
@@ -7939,7 +3825,7 @@
         <v>2855</v>
       </c>
       <c r="D233" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
@@ -7953,7 +3839,7 @@
         <v>2855</v>
       </c>
       <c r="D234" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
@@ -7967,7 +3853,7 @@
         <v>121</v>
       </c>
       <c r="D235" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
@@ -7981,7 +3867,7 @@
         <v>2855</v>
       </c>
       <c r="D236" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
@@ -7995,7 +3881,7 @@
         <v>3764</v>
       </c>
       <c r="D237" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
@@ -8009,7 +3895,7 @@
         <v>15</v>
       </c>
       <c r="D238" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
@@ -8023,7 +3909,7 @@
         <v>2855</v>
       </c>
       <c r="D239" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
@@ -8037,7 +3923,7 @@
         <v>121</v>
       </c>
       <c r="D240" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
@@ -8051,7 +3937,7 @@
         <v>121</v>
       </c>
       <c r="D241" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
@@ -8065,7 +3951,7 @@
         <v>121</v>
       </c>
       <c r="D242" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
@@ -8079,7 +3965,7 @@
         <v>4132</v>
       </c>
       <c r="D243" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
@@ -8093,7 +3979,7 @@
         <v>121</v>
       </c>
       <c r="D244" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
@@ -8107,7 +3993,7 @@
         <v>2855</v>
       </c>
       <c r="D245" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
@@ -8121,7 +4007,7 @@
         <v>2855</v>
       </c>
       <c r="D246" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
@@ -8135,7 +4021,7 @@
         <v>2855</v>
       </c>
       <c r="D247" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
@@ -8149,7 +4035,7 @@
         <v>2855</v>
       </c>
       <c r="D248" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
@@ -8163,7 +4049,7 @@
         <v>121</v>
       </c>
       <c r="D249" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
@@ -8177,7 +4063,7 @@
         <v>96</v>
       </c>
       <c r="D250" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
@@ -8191,7 +4077,7 @@
         <v>96</v>
       </c>
       <c r="D251" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
@@ -8205,7 +4091,7 @@
         <v>96</v>
       </c>
       <c r="D252" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
@@ -8219,7 +4105,7 @@
         <v>3764</v>
       </c>
       <c r="D253" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
@@ -8233,7 +4119,7 @@
         <v>96</v>
       </c>
       <c r="D254" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
@@ -8247,7 +4133,7 @@
         <v>121</v>
       </c>
       <c r="D255" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
@@ -8261,7 +4147,7 @@
         <v>3764</v>
       </c>
       <c r="D256" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
@@ -8275,7 +4161,7 @@
         <v>407</v>
       </c>
       <c r="D257" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
@@ -8289,7 +4175,7 @@
         <v>2855</v>
       </c>
       <c r="D258" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
@@ -8303,7 +4189,7 @@
         <v>1945</v>
       </c>
       <c r="D259" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
@@ -8317,7 +4203,7 @@
         <v>1945</v>
       </c>
       <c r="D260" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
@@ -8331,7 +4217,7 @@
         <v>3764</v>
       </c>
       <c r="D261" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
@@ -8345,7 +4231,7 @@
         <v>425</v>
       </c>
       <c r="D262" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
@@ -8359,7 +4245,7 @@
         <v>121</v>
       </c>
       <c r="D263" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
@@ -8373,7 +4259,7 @@
         <v>2855</v>
       </c>
       <c r="D264" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
@@ -8387,7 +4273,7 @@
         <v>121</v>
       </c>
       <c r="D265" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
@@ -8401,7 +4287,7 @@
         <v>121</v>
       </c>
       <c r="D266" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
@@ -8415,7 +4301,7 @@
         <v>96</v>
       </c>
       <c r="D267" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
@@ -8429,7 +4315,7 @@
         <v>3764</v>
       </c>
       <c r="D268" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
@@ -8443,7 +4329,7 @@
         <v>3764</v>
       </c>
       <c r="D269" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
@@ -8457,7 +4343,7 @@
         <v>121</v>
       </c>
       <c r="D270" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
@@ -8471,7 +4357,7 @@
         <v>2855</v>
       </c>
       <c r="D271" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
@@ -8485,7 +4371,7 @@
         <v>121</v>
       </c>
       <c r="D272" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
@@ -8496,10 +4382,10 @@
         <v>2023</v>
       </c>
       <c r="C273" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D273" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
@@ -8510,10 +4396,10 @@
         <v>2023</v>
       </c>
       <c r="C274" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
@@ -8524,10 +4410,10 @@
         <v>2023</v>
       </c>
       <c r="C275" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D275" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
@@ -8538,10 +4424,10 @@
         <v>2023</v>
       </c>
       <c r="C276" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
@@ -8552,10 +4438,10 @@
         <v>2023</v>
       </c>
       <c r="C277" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
@@ -8569,7 +4455,7 @@
         <v>121</v>
       </c>
       <c r="D278" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
@@ -8583,7 +4469,7 @@
         <v>146</v>
       </c>
       <c r="D279" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
@@ -8597,7 +4483,7 @@
         <v>121</v>
       </c>
       <c r="D280" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
@@ -8611,7 +4497,7 @@
         <v>3764</v>
       </c>
       <c r="D281" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
@@ -8625,7 +4511,7 @@
         <v>3764</v>
       </c>
       <c r="D282" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
@@ -8639,7 +4525,7 @@
         <v>2855</v>
       </c>
       <c r="D283" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
@@ -8653,7 +4539,7 @@
         <v>30</v>
       </c>
       <c r="D284" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
@@ -8667,7 +4553,7 @@
         <v>398</v>
       </c>
       <c r="D285" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
@@ -8681,7 +4567,7 @@
         <v>398</v>
       </c>
       <c r="D286" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
@@ -8695,7 +4581,7 @@
         <v>2944</v>
       </c>
       <c r="D287" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
@@ -8709,7 +4595,7 @@
         <v>2855</v>
       </c>
       <c r="D288" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
@@ -8723,7 +4609,7 @@
         <v>8</v>
       </c>
       <c r="D289" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
@@ -8737,7 +4623,7 @@
         <v>2855</v>
       </c>
       <c r="D290" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
@@ -8751,7 +4637,7 @@
         <v>398</v>
       </c>
       <c r="D291" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
@@ -8765,7 +4651,7 @@
         <v>398</v>
       </c>
       <c r="D292" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
@@ -8779,7 +4665,7 @@
         <v>2855</v>
       </c>
       <c r="D293" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
@@ -8793,7 +4679,7 @@
         <v>2855</v>
       </c>
       <c r="D294" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
@@ -8807,7 +4693,7 @@
         <v>121</v>
       </c>
       <c r="D295" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
@@ -8821,7 +4707,7 @@
         <v>121</v>
       </c>
       <c r="D296" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
@@ -8835,7 +4721,7 @@
         <v>121</v>
       </c>
       <c r="D297" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
@@ -8849,7 +4735,7 @@
         <v>121</v>
       </c>
       <c r="D298" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
@@ -8863,7 +4749,7 @@
         <v>8</v>
       </c>
       <c r="D299" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
@@ -8877,7 +4763,7 @@
         <v>2855</v>
       </c>
       <c r="D300" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
@@ -8891,7 +4777,7 @@
         <v>2855</v>
       </c>
       <c r="D301" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
@@ -8905,7 +4791,7 @@
         <v>398</v>
       </c>
       <c r="D302" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
@@ -8919,7 +4805,7 @@
         <v>2855</v>
       </c>
       <c r="D303" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
@@ -8933,7 +4819,7 @@
         <v>121</v>
       </c>
       <c r="D304" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
@@ -8947,7 +4833,7 @@
         <v>2855</v>
       </c>
       <c r="D305" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
@@ -8961,7 +4847,7 @@
         <v>121</v>
       </c>
       <c r="D306" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
@@ -8975,7 +4861,7 @@
         <v>30</v>
       </c>
       <c r="D307" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
@@ -8989,7 +4875,7 @@
         <v>2855</v>
       </c>
       <c r="D308" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
@@ -9003,7 +4889,7 @@
         <v>3764</v>
       </c>
       <c r="D309" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
@@ -9017,12 +4903,12 @@
         <v>2855</v>
       </c>
       <c r="D310" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B311">
         <v>2021</v>
@@ -9031,12 +4917,12 @@
         <v>2944</v>
       </c>
       <c r="D311" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B312">
         <v>2021</v>
@@ -9045,12 +4931,12 @@
         <v>121</v>
       </c>
       <c r="D312" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B313">
         <v>2022</v>
@@ -9059,12 +4945,12 @@
         <v>121</v>
       </c>
       <c r="D313" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B314">
         <v>2022</v>
@@ -9073,12 +4959,12 @@
         <v>407</v>
       </c>
       <c r="D314" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B315">
         <v>2022</v>
@@ -9087,12 +4973,12 @@
         <v>508</v>
       </c>
       <c r="D315" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B316">
         <v>2022</v>
@@ -9101,12 +4987,12 @@
         <v>15</v>
       </c>
       <c r="D316" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B317">
         <v>2022</v>
@@ -9115,12 +5001,12 @@
         <v>425</v>
       </c>
       <c r="D317" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B318">
         <v>2022</v>
@@ -9129,12 +5015,12 @@
         <v>398</v>
       </c>
       <c r="D318" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B319">
         <v>2022</v>
@@ -9143,12 +5029,12 @@
         <v>3764</v>
       </c>
       <c r="D319" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B320">
         <v>2022</v>
@@ -9157,12 +5043,12 @@
         <v>96</v>
       </c>
       <c r="D320" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B321">
         <v>2022</v>
@@ -9171,12 +5057,12 @@
         <v>2855</v>
       </c>
       <c r="D321" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B322">
         <v>2003</v>
@@ -9185,26 +5071,26 @@
         <v>121</v>
       </c>
       <c r="D322" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B323">
         <v>2002</v>
       </c>
       <c r="C323" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D323" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B324">
         <v>2001</v>
@@ -9213,12 +5099,12 @@
         <v>2780</v>
       </c>
       <c r="D324" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B325">
         <v>2002</v>
@@ -9227,12 +5113,12 @@
         <v>121</v>
       </c>
       <c r="D325" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B326">
         <v>2002</v>
@@ -9241,12 +5127,12 @@
         <v>121</v>
       </c>
       <c r="D326" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B327">
         <v>2001</v>
@@ -9255,12 +5141,12 @@
         <v>96</v>
       </c>
       <c r="D327" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B328">
         <v>2002</v>
@@ -9269,12 +5155,12 @@
         <v>96</v>
       </c>
       <c r="D328" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B329">
         <v>2002</v>
@@ -9283,12 +5169,12 @@
         <v>96</v>
       </c>
       <c r="D329" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B330">
         <v>2002</v>
@@ -9297,12 +5183,12 @@
         <v>96</v>
       </c>
       <c r="D330" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B331">
         <v>2003</v>
@@ -9311,26 +5197,26 @@
         <v>96</v>
       </c>
       <c r="D331" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B332">
         <v>2003</v>
       </c>
       <c r="C332" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D332" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B333">
         <v>2001</v>
@@ -9339,12 +5225,12 @@
         <v>96</v>
       </c>
       <c r="D333" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B334">
         <v>2003</v>
@@ -9353,12 +5239,12 @@
         <v>96</v>
       </c>
       <c r="D334" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B335">
         <v>2001</v>
@@ -9367,26 +5253,26 @@
         <v>1</v>
       </c>
       <c r="D335" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B336">
         <v>2005</v>
       </c>
       <c r="C336" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D336" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B337">
         <v>2005</v>
@@ -9395,12 +5281,12 @@
         <v>121</v>
       </c>
       <c r="D337" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B338">
         <v>2005</v>
@@ -9409,12 +5295,12 @@
         <v>407</v>
       </c>
       <c r="D338" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B339">
         <v>2005</v>
@@ -9423,12 +5309,12 @@
         <v>96</v>
       </c>
       <c r="D339" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B340">
         <v>2005</v>
@@ -9437,12 +5323,12 @@
         <v>96</v>
       </c>
       <c r="D340" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B341">
         <v>2005</v>
@@ -9451,12 +5337,12 @@
         <v>121</v>
       </c>
       <c r="D341" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B342">
         <v>2006</v>
@@ -9465,12 +5351,12 @@
         <v>121</v>
       </c>
       <c r="D342" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B343">
         <v>2006</v>
@@ -9479,12 +5365,12 @@
         <v>464</v>
       </c>
       <c r="D343" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B344">
         <v>2006</v>
@@ -9493,12 +5379,12 @@
         <v>2855</v>
       </c>
       <c r="D344" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B345">
         <v>2007</v>
@@ -9507,12 +5393,12 @@
         <v>121</v>
       </c>
       <c r="D345" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B346">
         <v>2007</v>
@@ -9521,12 +5407,12 @@
         <v>96</v>
       </c>
       <c r="D346" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B347">
         <v>2008</v>
@@ -9535,12 +5421,12 @@
         <v>121</v>
       </c>
       <c r="D347" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B348">
         <v>2008</v>
@@ -9549,12 +5435,12 @@
         <v>96</v>
       </c>
       <c r="D348" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B349">
         <v>2009</v>
@@ -9563,12 +5449,12 @@
         <v>121</v>
       </c>
       <c r="D349" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B350">
         <v>2009</v>
@@ -9577,12 +5463,12 @@
         <v>121</v>
       </c>
       <c r="D350" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B351">
         <v>2009</v>
@@ -9591,12 +5477,12 @@
         <v>9</v>
       </c>
       <c r="D351" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B352">
         <v>2010</v>
@@ -9605,12 +5491,12 @@
         <v>96</v>
       </c>
       <c r="D352" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="B353">
         <v>2010</v>
@@ -9619,12 +5505,12 @@
         <v>121</v>
       </c>
       <c r="D353" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="B354">
         <v>2011</v>
@@ -9633,12 +5519,12 @@
         <v>407</v>
       </c>
       <c r="D354" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="B355">
         <v>2012</v>
@@ -9647,12 +5533,12 @@
         <v>407</v>
       </c>
       <c r="D355" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="B356">
         <v>2010</v>
@@ -9661,12 +5547,12 @@
         <v>398</v>
       </c>
       <c r="D356" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B357">
         <v>2010</v>
@@ -9675,12 +5561,12 @@
         <v>96</v>
       </c>
       <c r="D357" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="B358">
         <v>2011</v>
@@ -9689,12 +5575,12 @@
         <v>2855</v>
       </c>
       <c r="D358" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="B359">
         <v>2011</v>
@@ -9703,7 +5589,7 @@
         <v>2855</v>
       </c>
       <c r="D359" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
